--- a/DataRepo/data/tests/full_tiny_study/study.xlsx
+++ b/DataRepo/data/tests/full_tiny_study/study.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-LOCAL/TRACEBASE/tracebase/DataRepo/data/tests/full_tiny_study/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/data/tests/full_tiny_study/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E61D14-2B0F-7844-B726-7F206D922084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E201D7-9176-664F-BBC1-E57D61CA1D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5600" yWindow="7700" windowWidth="38360" windowHeight="13720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5600" yWindow="7700" windowWidth="38360" windowHeight="13720" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study" sheetId="5" r:id="rId1"/>
@@ -545,9 +545,6 @@
     <t>BCAAs (VLI) {valine-[13C5,15N1][20]; leucine-[13C6,15N1][24]; isoleucine-[13C6,15N1][12]}</t>
   </si>
   <si>
-    <t>no manipulation besides what is already described in other fields</t>
-  </si>
-  <si>
     <t>This method involves the analysis of polar metabolites using HILIC on Waters Amide columns with basic buffer, coupled with high resolution mass spectrometry</t>
   </si>
   <si>
@@ -582,6 +579,9 @@
   </si>
   <si>
     <t>DataRepo/data/tests/full_tiny_study/glnfasted/glnfasted1_cor.xlsx</t>
+  </si>
+  <si>
+    <t>No manipulation besides what is already described in other fields.</t>
   </si>
 </sst>
 </file>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="2" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>171</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2510,7 +2510,7 @@
         <v>25</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.15">
@@ -2826,7 +2826,7 @@
         <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>41</v>
@@ -3012,7 +3012,7 @@
         <v>13</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3047,7 +3047,7 @@
         <v>13</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3082,7 +3082,7 @@
         <v>13</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -12501,7 +12501,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A1" s="22" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>109</v>
@@ -12577,12 +12577,12 @@
         <v>146</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>121</v>
@@ -12593,7 +12593,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>121</v>
@@ -12646,7 +12646,7 @@
         <v>110</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>123</v>
@@ -12757,13 +12757,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>173</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>174</v>
       </c>
       <c r="D8" t="s">
         <v>119</v>
@@ -12772,7 +12772,7 @@
         <v>141</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -12834,7 +12834,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
